--- a/software_inventory_kaspersky_inventory_20260915_123311.xlsx
+++ b/software_inventory_kaspersky_inventory_20260915_123311.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Unique Software" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Hosts per Software" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unique Software'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Hosts per Software'!$A$1:$V$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,9 +38,6 @@
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,18 +80,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,11 +459,11 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,11 +489,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Hosts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Hosts (sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Google Chrome</t>
@@ -521,7 +518,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>iOS Mobile Device Management plug-in</t>
@@ -546,7 +543,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Kaspersky Security Center Administration Server</t>
@@ -571,7 +568,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Kaspersky Security Center Network Agent</t>
@@ -596,7 +593,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Kaspersky Security Center Web Console</t>
@@ -621,7 +618,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Microsoft Edge</t>
@@ -646,7 +643,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2005 Redistributable - x64 8.0.61000</t>
@@ -671,7 +668,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2005 Redistributable - x86 8.0.61001</t>
@@ -696,7 +693,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2008 Redistributable - x64 9.0.30729.6161</t>
@@ -721,7 +718,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2008 Redistributable - x86 9.0.30729.6161</t>
@@ -746,7 +743,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2010 Redistributable - x64 10.0.40219</t>
@@ -771,7 +768,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2010 Redistributable - x86 10.0.40219</t>
@@ -796,7 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2012 Redistributable (x64) - 11.0.61030</t>
@@ -821,7 +818,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2012 Redistributable (x86) - 11.0.61030</t>
@@ -846,7 +843,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2013 Redistributable (x64) - 12.0.40664</t>
@@ -871,7 +868,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2013 Redistributable (x86) - 12.0.40664</t>
@@ -896,7 +893,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2015-2022 Redistributable (x64) - 14.40.33810</t>
@@ -921,7 +918,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Microsoft Visual C++ 2015-2022 Redistributable (x86) - 14.40.33810</t>
@@ -946,7 +943,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Microsoft Windows QFE</t>
@@ -963,7 +960,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>StartIsBack++</t>
@@ -988,7 +985,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>VMware Tools</t>
@@ -1013,7 +1010,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Windows Defender for Server</t>
@@ -1040,50 +1037,283 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Source JSON</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>kaspersky_inventory_20260915_123311.json</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Google Chrome [152.0.7977.83]</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iOS Mobile Device Management plug-in [14.2.0.47113]</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kaspersky Security Center Administration Server [15.1.0.22239]</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kaspersky Security Center Network Agent [16.0.0.254]</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kaspersky Security Center Web Console [15.1.1456]</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Edge [153.0.4234.32]</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2005 Redistributable - x64 8.0.61000 [8.0.61000]</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2005 Redistributable - x86 8.0.61001 [8.0.61001]</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2008 Redistributable - x64 9.0.30729.6161 [9.0.30729.6161]</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2008 Redistributable - x86 9.0.30729.6161 [9.0.30729.6161]</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2010 Redistributable - x64 10.0.40219 [10.0.40219]</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2010 Redistributable - x86 10.0.40219 [10.0.40219]</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2012 Redistributable (x64) - 11.0.61030 [11.0.61030.0]</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2012 Redistributable (x86) - 11.0.61030 [11.0.61030.0]</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2013 Redistributable (x64) - 12.0.40664 [12.0.40664.0]</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2013 Redistributable (x86) - 12.0.40664 [12.0.40664.0]</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2015-2022 Redistributable (x64) - 14.40.33810 [14.40.33810.0]</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Visual C++ 2015-2022 Redistributable (x86) - 14.40.33810 [14.40.33810.0]</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft Windows QFE</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>StartIsBack++ [2.8.9]</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>VMware Tools [12.5.0.24276846]</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Windows Defender for Server</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Generated</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-15T12:33:45.879497</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>OPREKIN-PC</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>OPREKIN-PC</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>OPREKIN-PC</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>WIN-SERVER-2022</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Total unique software (name+version)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>22</v>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>OPREKIN-PC</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>OPREKIN-PC</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>OPREKIN-PC</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>OPREKIN-PC</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>